--- a/Excel/ValetModelConfig.xlsx
+++ b/Excel/ValetModelConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="27">
   <si>
     <t>ID</t>
   </si>
@@ -78,22 +78,28 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>骷髅</t>
+    <t>小兵</t>
   </si>
   <si>
     <t>11001</t>
   </si>
   <si>
-    <t>神兽</t>
+    <t>魔兽</t>
   </si>
   <si>
     <t>21002,13005</t>
   </si>
   <si>
-    <t>月灵</t>
+    <t>月神</t>
   </si>
   <si>
     <t>3002</t>
+  </si>
+  <si>
+    <t>白虎</t>
+  </si>
+  <si>
+    <t>4004</t>
   </si>
   <si>
     <t>AttrList</t>
@@ -1071,7 +1077,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R54"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
@@ -1118,7 +1124,7 @@
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:18">
+    <row r="3" s="1" customFormat="1" ht="13.5" spans="1:18">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1162,7 +1168,7 @@
       <c r="Q3" s="2"/>
       <c r="R3" s="2"/>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:18">
+    <row r="4" s="1" customFormat="1" ht="13.5" spans="1:18">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
@@ -1206,7 +1212,7 @@
       <c r="Q4" s="2"/>
       <c r="R4" s="2"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:18">
+    <row r="5" s="1" customFormat="1" ht="13.5" spans="1:18">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
@@ -1339,7 +1345,7 @@
         <v>20</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1365,17 +1371,39 @@
       <c r="N8"/>
     </row>
     <row r="9" ht="24" customHeight="1" spans="3:14">
-      <c r="C9"/>
-      <c r="D9"/>
-      <c r="E9"/>
-      <c r="F9"/>
-      <c r="G9"/>
-      <c r="H9"/>
-      <c r="I9"/>
-      <c r="J9"/>
-      <c r="K9"/>
-      <c r="L9"/>
-      <c r="M9"/>
+      <c r="C9">
+        <v>4</v>
+      </c>
+      <c r="D9">
+        <v>3012</v>
+      </c>
+      <c r="E9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9">
+        <v>3</v>
+      </c>
+      <c r="G9">
+        <v>200</v>
+      </c>
+      <c r="H9">
+        <v>100</v>
+      </c>
+      <c r="I9">
+        <v>100</v>
+      </c>
+      <c r="J9">
+        <v>100</v>
+      </c>
+      <c r="K9">
+        <v>2</v>
+      </c>
+      <c r="L9">
+        <v>100</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>23</v>
+      </c>
       <c r="N9"/>
     </row>
     <row r="10" ht="24" customHeight="1" spans="3:14">
@@ -2008,7 +2036,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 E3 F3 H3 I3 K3 L3 M3 N3 D4 F4 H4 I4 K4 L4 M4 N4 D5 F5 G5 H5 I5 J5 K5 L5 M5 N5 C3:C5 E4:E5 G3:G4 J3:J4" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:N5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -2021,7 +2049,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:O38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
@@ -2067,7 +2095,7 @@
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:12">
+    <row r="3" s="1" customFormat="1" ht="13.5" spans="1:12">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -2077,10 +2105,10 @@
         <v>2</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -2091,7 +2119,7 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:12">
+    <row r="4" s="1" customFormat="1" ht="13.5" spans="1:12">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
@@ -2101,10 +2129,10 @@
         <v>2</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -2115,7 +2143,7 @@
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:12">
+    <row r="5" s="1" customFormat="1" ht="13.5" spans="1:12">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
@@ -2128,7 +2156,7 @@
         <v>15</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>15</v>
@@ -2439,7 +2467,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 E3:G3 E4 F4 G4 E5 F5 G5 C3:C5 D4:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:G5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/ValetModelConfig.xlsx
+++ b/Excel/ValetModelConfig.xlsx
@@ -60,7 +60,7 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>神将</t>
+    <t>英灵</t>
   </si>
   <si>
     <t>AttrList</t>
@@ -1159,9 +1159,11 @@
         <v>10</v>
       </c>
       <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="G6" s="4">
+        <v>5001</v>
+      </c>
       <c r="H6"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
@@ -1552,7 +1554,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5 G3:H5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
